--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583177</v>
       </c>
       <c r="B2" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136583178</v>
       </c>
       <c r="B3" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583177</v>
       </c>
       <c r="B2" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136583178</v>
       </c>
       <c r="B3" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583177</v>
       </c>
       <c r="B2" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136583178</v>
       </c>
       <c r="B3" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583177</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136583178</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,1350 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136583178</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136877191</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>773220</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7411629</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136877191</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136880273</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93415</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>773036</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7411291</v>
+      </c>
+      <c r="S5" t="n">
+        <v>46</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136880273</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136880272</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93437</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>773022</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7411322</v>
+      </c>
+      <c r="S6" t="n">
+        <v>23</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136880272</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136880265</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93395</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>773150</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7411111</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136880265</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136877190</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>773215</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7411618</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136877190</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136877192</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>773172</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7411708</v>
+      </c>
+      <c r="S9" t="n">
+        <v>47</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136877192</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136880266</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>773129</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7411738</v>
+      </c>
+      <c r="S10" t="n">
+        <v>17</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136880266</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136877188</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>773209</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7411246</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136877188</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136880270</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>772986</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7411352</v>
+      </c>
+      <c r="S12" t="n">
+        <v>24</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136880270</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136877189</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>773244</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7411300</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136877189</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136880271</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>772982</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7411363</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136880271</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136880264</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>773146</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7411109</v>
+      </c>
+      <c r="S15" t="n">
+        <v>23</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136880264</t>
         </is>
       </c>
     </row>
@@ -904,6 +2248,18 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136583177</v>
+        <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>93405</v>
+        <v>91117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Solberget, Lu lm</t>
+          <t>Iso Venetvaara, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>773121</v>
+        <v>773264</v>
       </c>
       <c r="R2" t="n">
-        <v>7411598</v>
+        <v>7411532</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583177</t>
+          <t>https://artportalen.se/Sighting/136933789</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136583178</v>
+        <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>93405</v>
+        <v>91117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,41 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Solberget, Lu lm</t>
+          <t>Iso Venetvaara, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>773121</v>
+        <v>773231</v>
       </c>
       <c r="R3" t="n">
-        <v>7411244</v>
+        <v>7411572</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,27 +887,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583178</t>
+          <t>https://artportalen.se/Sighting/136933790</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136877191</v>
+        <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>92166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Venetvaara, Lu lm</t>
+          <t>Iso Venetvaara, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>773220</v>
+        <v>773250</v>
       </c>
       <c r="R4" t="n">
-        <v>7411629</v>
+        <v>7411699</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,65 +999,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136877191</t>
+          <t>https://artportalen.se/Sighting/136933791</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136880273</v>
+        <v>136583177</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Venetvaara, Lu lm</t>
+          <t>Solberget, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>773036</v>
+        <v>773121</v>
       </c>
       <c r="R5" t="n">
-        <v>7411291</v>
+        <v>7411598</v>
       </c>
       <c r="S5" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,22 +1085,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,27 +1110,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136880273</t>
+          <t>https://artportalen.se/Sighting/136583177</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136880272</v>
+        <v>136583178</v>
       </c>
       <c r="B6" t="n">
-        <v>93437</v>
+        <v>93405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,37 +1138,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Venetvaara, Lu lm</t>
+          <t>Solberget, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>773022</v>
+        <v>773121</v>
       </c>
       <c r="R6" t="n">
-        <v>7411322</v>
+        <v>7411244</v>
       </c>
       <c r="S6" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,22 +1196,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,65 +1221,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136880272</t>
+          <t>https://artportalen.se/Sighting/136583178</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136880265</v>
+        <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93395</v>
+        <v>93405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6055</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Venetvaara, Lu lm</t>
+          <t>Iso Venetvaara, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>773150</v>
+        <v>773173</v>
       </c>
       <c r="R7" t="n">
-        <v>7411111</v>
+        <v>7411244</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,49 +1333,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136880265</t>
+          <t>https://artportalen.se/Sighting/136933785</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136877190</v>
+        <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>773215</v>
+        <v>773220</v>
       </c>
       <c r="R8" t="n">
-        <v>7411618</v>
+        <v>7411629</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,54 +1456,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136877190</t>
+          <t>https://artportalen.se/Sighting/136877191</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136877192</v>
+        <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Venetvaara, Lu lm</t>
+          <t>Iso Venetvaara, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>773172</v>
+        <v>773256</v>
       </c>
       <c r="R9" t="n">
-        <v>7411708</v>
+        <v>7411386</v>
       </c>
       <c r="S9" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,27 +1557,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136877192</t>
+          <t>https://artportalen.se/Sighting/136933786</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136880266</v>
+        <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,21 +1585,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1609,13 +1609,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>773129</v>
+        <v>773036</v>
       </c>
       <c r="R10" t="n">
-        <v>7411738</v>
+        <v>7411291</v>
       </c>
       <c r="S10" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,16 +1680,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136880266</t>
+          <t>https://artportalen.se/Sighting/136880273</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136877188</v>
+        <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>78879</v>
+        <v>93437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,21 +1697,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>5448</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1721,13 +1721,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>773209</v>
+        <v>773022</v>
       </c>
       <c r="R11" t="n">
-        <v>7411246</v>
+        <v>7411322</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,49 +1781,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Anders Lindmark</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Anders Lindmark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136877188</t>
+          <t>https://artportalen.se/Sighting/136880272</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136880270</v>
+        <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>78879</v>
+        <v>93395</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>6055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>772986</v>
+        <v>773150</v>
       </c>
       <c r="R12" t="n">
-        <v>7411352</v>
+        <v>7411111</v>
       </c>
       <c r="S12" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,51 +1904,51 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136880270</t>
+          <t>https://artportalen.se/Sighting/136880265</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136877189</v>
+        <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>58112</v>
+        <v>90895</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>6286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Venetvaara, Lu lm</t>
+          <t>Iso Venetvaara, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>773244</v>
+        <v>773260</v>
       </c>
       <c r="R13" t="n">
-        <v>7411300</v>
+        <v>7411402</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,49 +2005,49 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136877189</t>
+          <t>https://artportalen.se/Sighting/136933787</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136880271</v>
+        <v>136877190</v>
       </c>
       <c r="B14" t="n">
-        <v>80066</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>772982</v>
+        <v>773215</v>
       </c>
       <c r="R14" t="n">
-        <v>7411363</v>
+        <v>7411618</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,27 +2117,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136880271</t>
+          <t>https://artportalen.se/Sighting/136877190</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136880264</v>
+        <v>136877192</v>
       </c>
       <c r="B15" t="n">
-        <v>93442</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,21 +2145,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>232140</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2169,13 +2169,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>773146</v>
+        <v>773172</v>
       </c>
       <c r="R15" t="n">
-        <v>7411109</v>
+        <v>7411708</v>
       </c>
       <c r="S15" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,18 +2229,1148 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Lindmark</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136877192</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136880266</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>773129</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7411738</v>
+      </c>
+      <c r="S16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136880266</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136933792</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Iso Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>773149</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7411741</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933792</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136877188</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>773209</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7411246</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136877188</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136880270</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>772986</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7411352</v>
+      </c>
+      <c r="S19" t="n">
+        <v>24</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136880270</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136933793</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Iso Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>773002</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7411665</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Barkfläkning från födosök</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933793</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136877189</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>773244</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7411300</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Hannes Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136877189</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136880271</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>772982</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7411363</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136880271</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136933782</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Iso Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>773164</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7411012</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933782</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136880264</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>773146</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7411109</v>
+      </c>
+      <c r="S24" t="n">
+        <v>23</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Lindmark</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136880264</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136933781</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Iso Venetvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>773166</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7410976</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Ida Jansson, Severin Suess, Hannes Weiss, Anders Lindmark, Ignacio Gomez-Lobo</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933781</t>
         </is>
       </c>
     </row>
@@ -2260,6 +3390,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136583177</v>
       </c>
       <c r="B5" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136583178</v>
       </c>
       <c r="B6" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93395</v>
+        <v>93397</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136877190</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136877192</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>136880266</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136877188</v>
       </c>
       <c r="B18" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136880270</v>
       </c>
       <c r="B19" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>136880271</v>
       </c>
       <c r="B22" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136583177</v>
       </c>
       <c r="B5" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136583178</v>
       </c>
       <c r="B6" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136877190</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136877192</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>136880266</v>
       </c>
       <c r="B16" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136877188</v>
       </c>
       <c r="B18" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136880270</v>
       </c>
       <c r="B19" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>136880271</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136583177</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136583178</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136877190</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136877192</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>136880266</v>
       </c>
       <c r="B16" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136877188</v>
       </c>
       <c r="B18" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136880270</v>
       </c>
       <c r="B19" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>136880271</v>
       </c>
       <c r="B22" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136583177</v>
       </c>
       <c r="B5" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136583178</v>
       </c>
       <c r="B6" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136583177</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136583178</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136877190</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136877192</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>136880266</v>
       </c>
       <c r="B16" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136877188</v>
       </c>
       <c r="B18" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136880270</v>
       </c>
       <c r="B19" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>136880271</v>
       </c>
       <c r="B22" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136583177</v>
       </c>
       <c r="B5" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136583178</v>
       </c>
       <c r="B6" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136877190</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136877192</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>136880266</v>
       </c>
       <c r="B16" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136877188</v>
       </c>
       <c r="B18" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136880270</v>
       </c>
       <c r="B19" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>136880271</v>
       </c>
       <c r="B22" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136877190</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136877192</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>136880266</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136877188</v>
       </c>
       <c r="B18" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136880270</v>
       </c>
       <c r="B19" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136933793</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>136877189</v>
       </c>
       <c r="B21" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>136880271</v>
       </c>
       <c r="B22" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136877190</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136877192</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>136880266</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136877188</v>
       </c>
       <c r="B18" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136880270</v>
       </c>
       <c r="B19" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136933793</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>136877189</v>
       </c>
       <c r="B21" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>136880271</v>
       </c>
       <c r="B22" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -2723,11 +2723,7 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Iso Venetvaara, Lu lm</t>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93473</v>
+        <v>93476</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93473</v>
+        <v>93476</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136877190</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136877192</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>136880266</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136877188</v>
       </c>
       <c r="B18" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136880270</v>
       </c>
       <c r="B19" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136933793</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136877189</v>
       </c>
       <c r="B21" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136880271</v>
       </c>
       <c r="B22" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93476</v>
+        <v>93486</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93476</v>
+        <v>93486</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136877190</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136877192</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>136880266</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136877188</v>
       </c>
       <c r="B18" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136880270</v>
       </c>
       <c r="B19" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136933793</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136877189</v>
       </c>
       <c r="B21" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136880271</v>
       </c>
       <c r="B22" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93487</v>
+        <v>93492</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93487</v>
+        <v>93492</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93492</v>
+        <v>93494</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93492</v>
+        <v>93494</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136877190</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136877192</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>136880266</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136877188</v>
       </c>
       <c r="B18" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136880270</v>
       </c>
       <c r="B19" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136933793</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136877189</v>
       </c>
       <c r="B21" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136880271</v>
       </c>
       <c r="B22" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93494</v>
+        <v>93500</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93494</v>
+        <v>93500</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136877190</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136877192</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>136880266</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136877188</v>
       </c>
       <c r="B18" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136880270</v>
       </c>
       <c r="B19" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136880271</v>
       </c>
       <c r="B22" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93500</v>
+        <v>93512</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93500</v>
+        <v>93512</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>136877191</v>
       </c>
       <c r="B8" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136880273</v>
       </c>
       <c r="B10" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136880272</v>
       </c>
       <c r="B11" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136880265</v>
       </c>
       <c r="B12" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136877190</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>136877192</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>136880266</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136877188</v>
       </c>
       <c r="B18" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136880270</v>
       </c>
       <c r="B19" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>136880271</v>
       </c>
       <c r="B22" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>136880264</v>
       </c>
       <c r="B24" t="n">
-        <v>93512</v>
+        <v>93513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93512</v>
+        <v>93513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93513</v>
+        <v>93516</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92238</v>
+        <v>92239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93516</v>
+        <v>93517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 37043-2026 artfynd.xlsx
+++ b/artfynd/A 37043-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933789</v>
       </c>
       <c r="B2" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136933790</v>
       </c>
       <c r="B3" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136933791</v>
       </c>
       <c r="B4" t="n">
-        <v>92239</v>
+        <v>92242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136933785</v>
       </c>
       <c r="B7" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>136933786</v>
       </c>
       <c r="B9" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136933787</v>
       </c>
       <c r="B13" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>136933792</v>
       </c>
       <c r="B17" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>136933793</v>
       </c>
       <c r="B20" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>136933782</v>
       </c>
       <c r="B23" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>136933781</v>
       </c>
       <c r="B25" t="n">
-        <v>93517</v>
+        <v>93520</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
